--- a/data/trans_camb/P57_AF_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P57_AF_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,34; -4,59</t>
+          <t>-15,2; -4,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,52; 11,5</t>
+          <t>2,09; 12,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-21,81; -10,91</t>
+          <t>-21,78; -10,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 1,48</t>
+          <t>-9,15; 1,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,7; 15,08</t>
+          <t>4,9; 14,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,14; -6,51</t>
+          <t>-15,73; -6,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-10,65; -3,26</t>
+          <t>-10,51; -3,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,15; 12,07</t>
+          <t>4,93; 12,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-17,22; -10,07</t>
+          <t>-17,25; -9,82</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-21,84; -7,14</t>
+          <t>-22,06; -7,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,2; 17,9</t>
+          <t>2,99; 19,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-31,81; -16,86</t>
+          <t>-32,22; -16,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,01; 2,26</t>
+          <t>-13,07; 2,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,27; 23,1</t>
+          <t>7,1; 23,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-23,15; -10,25</t>
+          <t>-22,84; -9,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,41; -4,93</t>
+          <t>-15,43; -5,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,42; 18,45</t>
+          <t>7,16; 18,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-25,13; -15,43</t>
+          <t>-25,12; -15,15</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 6,47</t>
+          <t>-2,6; 6,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,99; 17,72</t>
+          <t>8,87; 17,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-36,09; -1,12</t>
+          <t>-36,0; -0,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 9,89</t>
+          <t>1,13; 9,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,02; 19,01</t>
+          <t>10,84; 19,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 3,21</t>
+          <t>-5,43; 3,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 6,64</t>
+          <t>0,46; 6,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,25; 17,12</t>
+          <t>10,88; 16,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-24,96; -0,7</t>
+          <t>-25,51; -0,93</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 11,1</t>
+          <t>-4,19; 11,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,29; 30,62</t>
+          <t>14,1; 30,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-58,72; -1,91</t>
+          <t>-58,92; -1,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 16,52</t>
+          <t>1,71; 16,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,95; 31,71</t>
+          <t>16,98; 31,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 5,44</t>
+          <t>-8,47; 5,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 11,08</t>
+          <t>0,73; 11,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,68; 28,64</t>
+          <t>17,43; 28,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-41,01; -1,18</t>
+          <t>-40,78; -1,53</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 7,89</t>
+          <t>-2,62; 8,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19,0; 28,72</t>
+          <t>18,79; 28,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 8,23</t>
+          <t>-3,12; 8,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 8,9</t>
+          <t>-1,2; 8,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,02; 28,49</t>
+          <t>19,43; 28,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 25,03</t>
+          <t>-5,39; 26,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 6,82</t>
+          <t>-0,62; 6,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>20,73; 27,15</t>
+          <t>20,38; 27,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 19,54</t>
+          <t>-1,98; 19,27</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 14,65</t>
+          <t>-4,47; 15,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>31,72; 53,96</t>
+          <t>31,24; 54,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 15,21</t>
+          <t>-5,35; 15,72</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 16,05</t>
+          <t>-1,96; 16,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>31,09; 51,85</t>
+          <t>31,76; 52,53</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 45,26</t>
+          <t>-9,12; 47,76</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 12,49</t>
+          <t>-0,97; 12,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>34,61; 49,32</t>
+          <t>34,07; 49,1</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 34,33</t>
+          <t>-3,46; 33,54</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,08; 12,11</t>
+          <t>3,89; 12,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,12; 13,86</t>
+          <t>5,22; 13,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,34; 0,12</t>
+          <t>-9,35; 0,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,35; 17,99</t>
+          <t>9,42; 17,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,56; 15,91</t>
+          <t>7,01; 15,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-18,13; -1,47</t>
+          <t>-17,74; -1,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,79; 14,1</t>
+          <t>7,75; 14,02</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,47; 13,63</t>
+          <t>7,14; 13,17</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-11,7; -1,99</t>
+          <t>-12,4; -2,12</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,03; 21,21</t>
+          <t>6,4; 21,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,31; 24,22</t>
+          <t>8,38; 24,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-15,28; 0,02</t>
+          <t>-15,51; 0,73</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15,53; 32,08</t>
+          <t>15,68; 32,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,63; 28,7</t>
+          <t>11,67; 27,84</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-30,49; -2,57</t>
+          <t>-30,07; -2,12</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,01; 24,79</t>
+          <t>12,74; 24,58</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>12,31; 23,77</t>
+          <t>11,83; 23,04</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-20,06; -3,49</t>
+          <t>-20,84; -3,7</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 3,62</t>
+          <t>-1,37; 3,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10,82; 15,61</t>
+          <t>10,97; 15,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-20,79; -3,97</t>
+          <t>-20,43; -3,79</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,04; 7,91</t>
+          <t>3,11; 7,76</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12,67; 17,11</t>
+          <t>12,67; 17,21</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 4,29</t>
+          <t>-7,13; 4,94</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,92; 5,12</t>
+          <t>1,76; 5,19</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12,5; 15,69</t>
+          <t>12,47; 15,73</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-11,64; -1,96</t>
+          <t>-12,31; -1,77</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 6,13</t>
+          <t>-2,23; 6,36</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>17,41; 26,34</t>
+          <t>17,65; 26,52</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-34,38; -6,52</t>
+          <t>-32,62; -6,3</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4,84; 13,22</t>
+          <t>4,96; 13,03</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>20,23; 28,42</t>
+          <t>20,3; 28,95</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 7,1</t>
+          <t>-11,44; 8,22</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,11; 8,48</t>
+          <t>2,82; 8,61</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>20,15; 26,15</t>
+          <t>20,29; 26,39</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-19,03; -3,2</t>
+          <t>-19,9; -2,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P57_AF_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P57_AF_R-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-15,93</t>
+          <t>-14,38</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-11,51</t>
+          <t>-11,46</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-13,65</t>
+          <t>-12,87</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,2; -4,65</t>
+          <t>-15,06; -4,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,09; 12,39</t>
+          <t>1,91; 12,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-21,78; -10,45</t>
+          <t>-20,06; -9,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 1,27</t>
+          <t>-9,51; 1,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,9; 14,86</t>
+          <t>5,97; 15,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,73; -6,37</t>
+          <t>-15,78; -6,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-10,51; -3,37</t>
+          <t>-10,31; -3,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,93; 12,25</t>
+          <t>5,46; 12,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-17,25; -9,82</t>
+          <t>-16,64; -9,41</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-23,81%</t>
+          <t>-21,49%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-17,1%</t>
+          <t>-17,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-20,33%</t>
+          <t>-19,18%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-22,06; -7,22</t>
+          <t>-21,86; -7,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,99; 19,41</t>
+          <t>2,76; 18,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-32,22; -16,5</t>
+          <t>-28,72; -14,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,07; 2,01</t>
+          <t>-13,66; 1,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,1; 23,0</t>
+          <t>8,52; 23,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-22,84; -9,91</t>
+          <t>-22,87; -10,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,43; -5,1</t>
+          <t>-15,17; -5,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,16; 18,73</t>
+          <t>7,92; 18,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-25,12; -15,15</t>
+          <t>-24,22; -14,36</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-14,47</t>
+          <t>-2,2</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-1,18</t>
+          <t>0,08</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-8,68</t>
+          <t>-1,04</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 6,47</t>
+          <t>-3,01; 5,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,87; 17,61</t>
+          <t>9,02; 17,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-36,0; -0,61</t>
+          <t>-7,09; 2,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 9,74</t>
+          <t>0,97; 9,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,84; 19,03</t>
+          <t>10,47; 18,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 3,06</t>
+          <t>-4,09; 4,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 6,82</t>
+          <t>0,36; 6,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,88; 16,95</t>
+          <t>11,26; 16,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-25,51; -0,93</t>
+          <t>-3,99; 2,19</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-24,02%</t>
+          <t>-3,66%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-1,89%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-14,16%</t>
+          <t>-1,7%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 11,33</t>
+          <t>-4,79; 10,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,1; 30,58</t>
+          <t>14,46; 30,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-58,92; -1,05</t>
+          <t>-11,32; 4,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 16,14</t>
+          <t>1,46; 16,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,98; 31,92</t>
+          <t>16,0; 31,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 5,03</t>
+          <t>-6,38; 7,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 11,42</t>
+          <t>0,56; 11,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,43; 28,51</t>
+          <t>17,93; 28,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-40,78; -1,53</t>
+          <t>-6,36; 3,68</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,37</t>
+          <t>3,84</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,06</t>
+          <t>-0,01</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5,14</t>
+          <t>1,91</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 8,62</t>
+          <t>-2,32; 7,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,79; 28,82</t>
+          <t>19,05; 28,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 8,37</t>
+          <t>-2,2; 9,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 8,86</t>
+          <t>-1,4; 9,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,43; 28,82</t>
+          <t>19,31; 28,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 26,68</t>
+          <t>-4,79; 5,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 6,86</t>
+          <t>-0,83; 6,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>20,38; 27,07</t>
+          <t>20,49; 27,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 19,27</t>
+          <t>-1,91; 5,45</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>-0,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 15,84</t>
+          <t>-3,96; 15,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>31,24; 54,02</t>
+          <t>31,8; 53,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 15,72</t>
+          <t>-3,79; 16,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 16,0</t>
+          <t>-2,34; 17,03</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>31,76; 52,53</t>
+          <t>31,48; 52,34</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 47,76</t>
+          <t>-7,88; 9,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 12,48</t>
+          <t>-1,41; 12,46</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>34,07; 49,1</t>
+          <t>34,54; 50,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 33,54</t>
+          <t>-3,18; 9,89</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-4,52</t>
+          <t>-3,34</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-6,78</t>
+          <t>-2,55</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-5,77</t>
+          <t>-2,92</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,89; 12,43</t>
+          <t>3,53; 12,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,22; 13,66</t>
+          <t>4,95; 13,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 0,49</t>
+          <t>-8,13; 1,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,42; 17,9</t>
+          <t>9,62; 17,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,01; 15,55</t>
+          <t>6,52; 15,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-17,74; -1,16</t>
+          <t>-6,68; 1,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,75; 14,02</t>
+          <t>7,92; 13,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,14; 13,17</t>
+          <t>7,17; 13,44</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-12,4; -2,12</t>
+          <t>-5,91; 0,1</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-7,61%</t>
+          <t>-5,61%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-11,64%</t>
+          <t>-4,37%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-9,8%</t>
+          <t>-4,97%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,4; 21,72</t>
+          <t>5,63; 21,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,38; 24,0</t>
+          <t>7,72; 24,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-15,51; 0,73</t>
+          <t>-13,25; 2,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15,68; 32,0</t>
+          <t>15,92; 31,99</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,67; 27,84</t>
+          <t>10,63; 27,04</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-30,07; -2,12</t>
+          <t>-10,97; 2,89</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,74; 24,58</t>
+          <t>13,28; 24,16</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,83; 23,04</t>
+          <t>11,91; 23,63</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-20,84; -3,7</t>
+          <t>-9,77; 0,19</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-8,8</t>
+          <t>-3,7</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-2,92</t>
+          <t>-3,06</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-5,78</t>
+          <t>-3,37</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 3,76</t>
+          <t>-1,0; 3,52</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10,97; 15,62</t>
+          <t>10,95; 15,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-20,43; -3,79</t>
+          <t>-6,47; -1,2</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,11; 7,76</t>
+          <t>3,27; 7,91</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12,67; 17,21</t>
+          <t>12,68; 17,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 4,94</t>
+          <t>-5,31; -0,77</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,76; 5,19</t>
+          <t>1,79; 5,08</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12,47; 15,73</t>
+          <t>12,37; 15,65</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-12,31; -1,77</t>
+          <t>-5,18; -1,71</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-14,51%</t>
+          <t>-6,09%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-4,77%</t>
+          <t>-4,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-9,48%</t>
+          <t>-5,52%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 6,36</t>
+          <t>-1,66; 5,88</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>17,65; 26,52</t>
+          <t>17,75; 26,05</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-32,62; -6,3</t>
+          <t>-10,53; -1,96</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4,96; 13,03</t>
+          <t>5,19; 13,07</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>20,3; 28,95</t>
+          <t>20,29; 28,5</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 8,22</t>
+          <t>-8,45; -1,28</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,82; 8,61</t>
+          <t>2,91; 8,43</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>20,29; 26,39</t>
+          <t>19,85; 26,0</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-19,9; -2,9</t>
+          <t>-8,4; -2,82</t>
         </is>
       </c>
     </row>
